--- a/artfynd/A 8451-2026 artfynd.xlsx
+++ b/artfynd/A 8451-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128732470</v>
       </c>
       <c r="B2" t="n">
-        <v>57831</v>
+        <v>57990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8451-2026 artfynd.xlsx
+++ b/artfynd/A 8451-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128732470</v>
       </c>
       <c r="B2" t="n">
-        <v>57990</v>
+        <v>57991</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8451-2026 artfynd.xlsx
+++ b/artfynd/A 8451-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128732470</v>
       </c>
       <c r="B2" t="n">
-        <v>57991</v>
+        <v>57992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8451-2026 artfynd.xlsx
+++ b/artfynd/A 8451-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128732470</v>
       </c>
       <c r="B2" t="n">
-        <v>57992</v>
+        <v>57995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8451-2026 artfynd.xlsx
+++ b/artfynd/A 8451-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128732470</v>
       </c>
       <c r="B2" t="n">
-        <v>57995</v>
+        <v>57996</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christina Wallin, Torbjörn Wallin</t>
+          <t>Torbjörn Wallin, Christina Wallin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 8451-2026 artfynd.xlsx
+++ b/artfynd/A 8451-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128732470</v>
       </c>
       <c r="B2" t="n">
-        <v>57996</v>
+        <v>58002</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Torbjörn Wallin, Christina Wallin</t>
+          <t>Christina Wallin, Torbjörn Wallin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 8451-2026 artfynd.xlsx
+++ b/artfynd/A 8451-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128732470</v>
       </c>
       <c r="B2" t="n">
-        <v>58002</v>
+        <v>58003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8451-2026 artfynd.xlsx
+++ b/artfynd/A 8451-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128732470</v>
       </c>
       <c r="B2" t="n">
-        <v>58003</v>
+        <v>58006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8451-2026 artfynd.xlsx
+++ b/artfynd/A 8451-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128732470</v>
       </c>
       <c r="B2" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christina Wallin, Torbjörn Wallin</t>
+          <t>Torbjörn Wallin, Christina Wallin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 8451-2026 artfynd.xlsx
+++ b/artfynd/A 8451-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128732470</v>
       </c>
       <c r="B2" t="n">
-        <v>58008</v>
+        <v>58011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Torbjörn Wallin, Christina Wallin</t>
+          <t>Christina Wallin, Torbjörn Wallin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 8451-2026 artfynd.xlsx
+++ b/artfynd/A 8451-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128732470</v>
+        <v>70455748</v>
       </c>
       <c r="B2" t="n">
-        <v>58011</v>
+        <v>58057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -705,34 +705,25 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder Lövtjärn, Källsjön, Gstr</t>
+          <t>Knottåsen, Källsjön, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566732</v>
+        <v>566755</v>
       </c>
       <c r="R2" t="n">
-        <v>6763111</v>
+        <v>6763247</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +747,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flög över vägen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,15 +782,138 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Lena Berg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Lena Berg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128732470</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Söder Lövtjärn, Källsjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>566732</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6763111</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Christina Wallin</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Christina Wallin, Torbjörn Wallin</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
